--- a/results/res_bef_gauss.xlsx
+++ b/results/res_bef_gauss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,1367 +465,772 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>575.78226</v>
+        <v>464.42791</v>
       </c>
       <c r="B2" t="n">
-        <v>1.555002116243052</v>
+        <v>1.616874082439316</v>
       </c>
       <c r="C2" t="n">
-        <v>1.573096793387012</v>
+        <v>1.831488508184895</v>
       </c>
       <c r="D2" t="n">
-        <v>1.578881953277075</v>
+        <v>1.626049048595725</v>
       </c>
       <c r="E2" t="n">
-        <v>1.237570048534098</v>
+        <v>1.06005865632238</v>
       </c>
       <c r="F2" t="n">
-        <v>1.098140491140402</v>
+        <v>1.010837852966876</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7201850641701111</v>
+        <v>1.07748864970381</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3870356535654686</v>
+        <v>1.099929460892934</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4347483447432323</v>
+        <v>1.205600322215203</v>
       </c>
       <c r="J2" t="n">
-        <v>0.346420511012979</v>
+        <v>0.9717363778566411</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2303383178967767</v>
+        <v>0.9490106298303616</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>575.87308</v>
+        <v>464.52582</v>
       </c>
       <c r="B3" t="n">
-        <v>2.729102281289442</v>
+        <v>1.907286919269258</v>
       </c>
       <c r="C3" t="n">
-        <v>3.256006674452642</v>
+        <v>1.911858258673608</v>
       </c>
       <c r="D3" t="n">
-        <v>2.916890225492299</v>
+        <v>1.434191824835925</v>
       </c>
       <c r="E3" t="n">
-        <v>2.600644559559588</v>
+        <v>1.259296516551307</v>
       </c>
       <c r="F3" t="n">
-        <v>1.726965570337926</v>
+        <v>0.9397773338548868</v>
       </c>
       <c r="G3" t="n">
-        <v>1.166070689172798</v>
+        <v>1.24533101382799</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9884852313418331</v>
+        <v>1.309135067803524</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6021037539215521</v>
+        <v>1.65443546900398</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4182171299384888</v>
+        <v>1.784513803838143</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4407518088892156</v>
+        <v>2.035162736537704</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>575.96389</v>
+        <v>464.62373</v>
       </c>
       <c r="B4" t="n">
-        <v>2.530032524127213</v>
+        <v>0.6117081158261931</v>
       </c>
       <c r="C4" t="n">
-        <v>2.84697456735467</v>
+        <v>0.6388548420503363</v>
       </c>
       <c r="D4" t="n">
-        <v>2.462138412482929</v>
+        <v>0.3736279743954678</v>
       </c>
       <c r="E4" t="n">
-        <v>2.147277619906905</v>
+        <v>0.5231793335942674</v>
       </c>
       <c r="F4" t="n">
-        <v>1.421047088132916</v>
+        <v>0.6513639048558969</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9765788514343828</v>
+        <v>0.6586867756555358</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6759341658042364</v>
+        <v>0.6290035006932939</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2068624607391295</v>
+        <v>0.6624956378530319</v>
       </c>
       <c r="J4" t="n">
-        <v>0.148436307807193</v>
+        <v>0.9681780344263682</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1613047970846678</v>
+        <v>1.368641725089236</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>576.0546900000001</v>
+        <v>464.72163</v>
       </c>
       <c r="B5" t="n">
-        <v>2.214010088703607</v>
+        <v>2.095466929972972</v>
       </c>
       <c r="C5" t="n">
-        <v>2.431014779851329</v>
+        <v>1.89833357481497</v>
       </c>
       <c r="D5" t="n">
-        <v>2.375642757436892</v>
+        <v>1.683641734263317</v>
       </c>
       <c r="E5" t="n">
-        <v>2.025600077848875</v>
+        <v>1.386423804485865</v>
       </c>
       <c r="F5" t="n">
-        <v>1.504904295790656</v>
+        <v>1.049961995522002</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6699005079829332</v>
+        <v>0.8721586766801971</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1061880789960268</v>
+        <v>0.891492739248489</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07066795202498867</v>
+        <v>0.8906874888291514</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.04315547137234567</v>
+        <v>0.7543867765999986</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.006688814103624144</v>
+        <v>0.7988849147725854</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>576.14549</v>
+        <v>464.81952</v>
       </c>
       <c r="B6" t="n">
-        <v>1.697939108010444</v>
+        <v>5.193447238672686</v>
       </c>
       <c r="C6" t="n">
-        <v>2.065563615732485</v>
+        <v>4.951552591454089</v>
       </c>
       <c r="D6" t="n">
-        <v>1.852921136894992</v>
+        <v>4.687385359278955</v>
       </c>
       <c r="E6" t="n">
-        <v>1.235447330454679</v>
+        <v>4.068683705992004</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5401599070875768</v>
+        <v>3.066160407026262</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.04737196091246753</v>
+        <v>3.012741537319797</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1152955977502416</v>
+        <v>2.947164494321753</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08807364104216209</v>
+        <v>2.342757126674835</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06169298100938751</v>
+        <v>1.412130872279445</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06101298557634037</v>
+        <v>1.028377485829837</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>576.23628</v>
+        <v>464.91741</v>
       </c>
       <c r="B7" t="n">
-        <v>2.614407848720014</v>
+        <v>6.721739068705429</v>
       </c>
       <c r="C7" t="n">
-        <v>2.586712776499382</v>
+        <v>6.47251032184439</v>
       </c>
       <c r="D7" t="n">
-        <v>1.990975712869342</v>
+        <v>6.309454280485721</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9505970047848179</v>
+        <v>5.862640401217222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.82368369487751</v>
+        <v>5.297493074592421</v>
       </c>
       <c r="G7" t="n">
-        <v>0.70044806755606</v>
+        <v>5.032369984232732</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9517151976812916</v>
+        <v>4.267269176005608</v>
       </c>
       <c r="I7" t="n">
-        <v>0.793106029071064</v>
+        <v>3.455993559658316</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5556468389904079</v>
+        <v>2.580140421852378</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3533584583419455</v>
+        <v>1.833790378281226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>576.32707</v>
+        <v>465.0153</v>
       </c>
       <c r="B8" t="n">
-        <v>4.074345166544244</v>
+        <v>7.037469559864801</v>
       </c>
       <c r="C8" t="n">
-        <v>3.730110174276748</v>
+        <v>5.858888770850081</v>
       </c>
       <c r="D8" t="n">
-        <v>3.322517453526482</v>
+        <v>4.89888195724572</v>
       </c>
       <c r="E8" t="n">
-        <v>2.007036129704621</v>
+        <v>4.026955410399759</v>
       </c>
       <c r="F8" t="n">
-        <v>1.84309673908635</v>
+        <v>3.740685583689937</v>
       </c>
       <c r="G8" t="n">
-        <v>1.498791997518082</v>
+        <v>3.673248569468972</v>
       </c>
       <c r="H8" t="n">
-        <v>1.397538205756962</v>
+        <v>3.459341625689374</v>
       </c>
       <c r="I8" t="n">
-        <v>1.083809021308782</v>
+        <v>3.512805419780348</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7252976153424309</v>
+        <v>3.372181226086867</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2580692424323933</v>
+        <v>2.783099892296755</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>576.41785</v>
+        <v>465.11318</v>
       </c>
       <c r="B9" t="n">
-        <v>5.177386297658381</v>
+        <v>1.950598538627284</v>
       </c>
       <c r="C9" t="n">
-        <v>5.339048759410415</v>
+        <v>1.677310233697067</v>
       </c>
       <c r="D9" t="n">
-        <v>4.74290950265924</v>
+        <v>1.399787015803047</v>
       </c>
       <c r="E9" t="n">
-        <v>3.058906742019878</v>
+        <v>1.314823827331311</v>
       </c>
       <c r="F9" t="n">
-        <v>1.961877677222083</v>
+        <v>1.274412239572147</v>
       </c>
       <c r="G9" t="n">
-        <v>1.434757919665527</v>
+        <v>1.209797194995583</v>
       </c>
       <c r="H9" t="n">
-        <v>1.273841528856948</v>
+        <v>1.252201682973006</v>
       </c>
       <c r="I9" t="n">
-        <v>1.185922624018098</v>
+        <v>1.337366533966828</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8931326381062017</v>
+        <v>1.292360204037788</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3194136068983769</v>
+        <v>1.192220922237316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>576.50862</v>
+        <v>465.21105</v>
       </c>
       <c r="B10" t="n">
-        <v>5.442459176983326</v>
+        <v>1.046161857157886</v>
       </c>
       <c r="C10" t="n">
-        <v>5.235567808462585</v>
+        <v>0.9002285699389547</v>
       </c>
       <c r="D10" t="n">
-        <v>4.235605582211579</v>
+        <v>1.416746392461866</v>
       </c>
       <c r="E10" t="n">
-        <v>3.290177671523894</v>
+        <v>1.445868578543377</v>
       </c>
       <c r="F10" t="n">
-        <v>2.683564113527157</v>
+        <v>1.866088200438224</v>
       </c>
       <c r="G10" t="n">
-        <v>2.455628039455443</v>
+        <v>1.812179920506291</v>
       </c>
       <c r="H10" t="n">
-        <v>1.667283255844681</v>
+        <v>1.560144068176671</v>
       </c>
       <c r="I10" t="n">
-        <v>1.346358652091952</v>
+        <v>1.331844684470182</v>
       </c>
       <c r="J10" t="n">
-        <v>1.375125368384612</v>
+        <v>1.377819841897729</v>
       </c>
       <c r="K10" t="n">
-        <v>1.750845080485182</v>
+        <v>0.957258207288372</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>576.59939</v>
+        <v>465.30891</v>
       </c>
       <c r="B11" t="n">
-        <v>11.13197785776529</v>
+        <v>2.44353917501173</v>
       </c>
       <c r="C11" t="n">
-        <v>10.02950670469368</v>
+        <v>2.133700288772345</v>
       </c>
       <c r="D11" t="n">
-        <v>8.136293622635931</v>
+        <v>1.939576494356846</v>
       </c>
       <c r="E11" t="n">
-        <v>6.058744415171154</v>
+        <v>1.678013475311149</v>
       </c>
       <c r="F11" t="n">
-        <v>4.839733583956194</v>
+        <v>1.865002808828722</v>
       </c>
       <c r="G11" t="n">
-        <v>3.638536761438652</v>
+        <v>2.145568904271579</v>
       </c>
       <c r="H11" t="n">
-        <v>2.983132877070013</v>
+        <v>2.367206307344393</v>
       </c>
       <c r="I11" t="n">
-        <v>1.70025984407445</v>
+        <v>2.301960196447748</v>
       </c>
       <c r="J11" t="n">
-        <v>1.06986947835605</v>
+        <v>2.472229481055499</v>
       </c>
       <c r="K11" t="n">
-        <v>1.426761292088015</v>
+        <v>1.808896626468707</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>576.69015</v>
+        <v>465.40677</v>
       </c>
       <c r="B12" t="n">
-        <v>1.836062671523826</v>
+        <v>4.189509693906817</v>
       </c>
       <c r="C12" t="n">
-        <v>2.70260907066292</v>
+        <v>4.227575263912804</v>
       </c>
       <c r="D12" t="n">
-        <v>3.940892056098382</v>
+        <v>3.980895290182972</v>
       </c>
       <c r="E12" t="n">
-        <v>4.717212615066481</v>
+        <v>3.838050293814783</v>
       </c>
       <c r="F12" t="n">
-        <v>5.096554151262707</v>
+        <v>3.268757424034621</v>
       </c>
       <c r="G12" t="n">
-        <v>4.290907961242003</v>
+        <v>2.672806218061782</v>
       </c>
       <c r="H12" t="n">
-        <v>3.537418201952302</v>
+        <v>2.602438937588186</v>
       </c>
       <c r="I12" t="n">
-        <v>2.422141453152167</v>
+        <v>1.924347874916704</v>
       </c>
       <c r="J12" t="n">
-        <v>1.032467648778963</v>
+        <v>1.458093225110884</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5795456703049729</v>
+        <v>1.017575782225592</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>576.7809099999999</v>
+        <v>465.50462</v>
       </c>
       <c r="B13" t="n">
-        <v>34.80690793131281</v>
+        <v>-0.02418778497633989</v>
       </c>
       <c r="C13" t="n">
-        <v>28.08938061125473</v>
+        <v>0.1907158469814406</v>
       </c>
       <c r="D13" t="n">
-        <v>20.8775915880325</v>
+        <v>0.04432363221344199</v>
       </c>
       <c r="E13" t="n">
-        <v>11.61769542595052</v>
+        <v>-0.3199908500773842</v>
       </c>
       <c r="F13" t="n">
-        <v>5.129998855122446</v>
+        <v>-0.5970396742191743</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05292773532005363</v>
+        <v>-0.0568122693524262</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9989095396328631</v>
+        <v>0.1036630413401966</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9516734053637164</v>
+        <v>0.07920048312652621</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8342110312891055</v>
+        <v>0.4548619391054533</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06061027823209946</v>
+        <v>0.9562650465509795</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>576.87166</v>
+        <v>465.60247</v>
       </c>
       <c r="B14" t="n">
-        <v>204.2961690817253</v>
+        <v>6.602547894451257</v>
       </c>
       <c r="C14" t="n">
-        <v>180.981022618771</v>
+        <v>6.32194520450274</v>
       </c>
       <c r="D14" t="n">
-        <v>149.8940849640156</v>
+        <v>5.319551141844216</v>
       </c>
       <c r="E14" t="n">
-        <v>112.9672737675069</v>
+        <v>5.148548343835939</v>
       </c>
       <c r="F14" t="n">
-        <v>80.46301368739056</v>
+        <v>4.152618555999058</v>
       </c>
       <c r="G14" t="n">
-        <v>49.22550367794262</v>
+        <v>3.429074355491765</v>
       </c>
       <c r="H14" t="n">
-        <v>27.92539802124432</v>
+        <v>2.618528258338481</v>
       </c>
       <c r="I14" t="n">
-        <v>10.7316389770705</v>
+        <v>2.00816665274171</v>
       </c>
       <c r="J14" t="n">
-        <v>2.87223675912498</v>
+        <v>1.430796733421783</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5895039475408763</v>
+        <v>1.230015124703557</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>576.96241</v>
+        <v>465.70031</v>
       </c>
       <c r="B15" t="n">
-        <v>362.5086784984444</v>
+        <v>103.4643350954287</v>
       </c>
       <c r="C15" t="n">
-        <v>341.5920389830492</v>
+        <v>101.047511994025</v>
       </c>
       <c r="D15" t="n">
-        <v>307.6398549021986</v>
+        <v>96.73628408982363</v>
       </c>
       <c r="E15" t="n">
-        <v>258.5299681102818</v>
+        <v>91.43914675886943</v>
       </c>
       <c r="F15" t="n">
-        <v>207.1245792293589</v>
+        <v>83.08114038473346</v>
       </c>
       <c r="G15" t="n">
-        <v>146.3882576029659</v>
+        <v>71.22957763703675</v>
       </c>
       <c r="H15" t="n">
-        <v>94.5636903858743</v>
+        <v>59.96740163363487</v>
       </c>
       <c r="I15" t="n">
-        <v>46.24868904304201</v>
+        <v>49.40905003627135</v>
       </c>
       <c r="J15" t="n">
-        <v>17.77616772502299</v>
+        <v>38.63770242907146</v>
       </c>
       <c r="K15" t="n">
-        <v>3.830656281309644</v>
+        <v>27.81886259787616</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>577.05315</v>
+        <v>465.79815</v>
       </c>
       <c r="B16" t="n">
-        <v>705.7379394490423</v>
+        <v>162.9633269764067</v>
       </c>
       <c r="C16" t="n">
-        <v>645.9266125275075</v>
+        <v>160.9906248054756</v>
       </c>
       <c r="D16" t="n">
-        <v>558.8622055554079</v>
+        <v>156.1147744619653</v>
       </c>
       <c r="E16" t="n">
-        <v>438.2776270044089</v>
+        <v>146.5867705982202</v>
       </c>
       <c r="F16" t="n">
-        <v>322.1313012495995</v>
+        <v>134.7093343616288</v>
       </c>
       <c r="G16" t="n">
-        <v>205.6116890325112</v>
+        <v>117.4976742816686</v>
       </c>
       <c r="H16" t="n">
-        <v>118.0647323508001</v>
+        <v>100.0412449326923</v>
       </c>
       <c r="I16" t="n">
-        <v>51.43860732652585</v>
+        <v>82.49224597407029</v>
       </c>
       <c r="J16" t="n">
-        <v>16.90338347955547</v>
+        <v>66.37267017510845</v>
       </c>
       <c r="K16" t="n">
-        <v>2.346326283707405</v>
+        <v>49.08099216733937</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>577.14388</v>
+        <v>465.89598</v>
       </c>
       <c r="B17" t="n">
-        <v>2160.673176454443</v>
+        <v>40.40739002315999</v>
       </c>
       <c r="C17" t="n">
-        <v>1967.574426099322</v>
+        <v>41.25288962810616</v>
       </c>
       <c r="D17" t="n">
-        <v>1680.040207985835</v>
+        <v>40.91279871954287</v>
       </c>
       <c r="E17" t="n">
-        <v>1308.137530665851</v>
+        <v>38.64266513192295</v>
       </c>
       <c r="F17" t="n">
-        <v>946.0816971328346</v>
+        <v>36.99086687102577</v>
       </c>
       <c r="G17" t="n">
-        <v>592.751801268702</v>
+        <v>33.43824180458905</v>
       </c>
       <c r="H17" t="n">
-        <v>325.9961377049053</v>
+        <v>29.50187351870138</v>
       </c>
       <c r="I17" t="n">
-        <v>131.73141547505</v>
+        <v>24.87853585102056</v>
       </c>
       <c r="J17" t="n">
-        <v>42.31732889057339</v>
+        <v>20.9351284680306</v>
       </c>
       <c r="K17" t="n">
-        <v>4.114642379160703</v>
+        <v>16.9796094171516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>577.2346</v>
+        <v>465.9938</v>
       </c>
       <c r="B18" t="n">
-        <v>3365.227066939869</v>
+        <v>-4.843391672475898</v>
       </c>
       <c r="C18" t="n">
-        <v>3334.700764742209</v>
+        <v>-4.813852735513228</v>
       </c>
       <c r="D18" t="n">
-        <v>3132.151117940787</v>
+        <v>-4.369061447367394</v>
       </c>
       <c r="E18" t="n">
-        <v>2714.884350813346</v>
+        <v>-4.507002136941724</v>
       </c>
       <c r="F18" t="n">
-        <v>2160.966624083319</v>
+        <v>-3.770649476522812</v>
       </c>
       <c r="G18" t="n">
-        <v>1470.547437057246</v>
+        <v>-3.61776480124389</v>
       </c>
       <c r="H18" t="n">
-        <v>864.5467819412651</v>
+        <v>-3.340369674876106</v>
       </c>
       <c r="I18" t="n">
-        <v>374.7186432441112</v>
+        <v>-2.743604236094432</v>
       </c>
       <c r="J18" t="n">
-        <v>121.8135296718249</v>
+        <v>-2.31469401526503</v>
       </c>
       <c r="K18" t="n">
-        <v>13.23048807258822</v>
+        <v>-1.702051303019604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>577.32532</v>
+        <v>466.09162</v>
       </c>
       <c r="B19" t="n">
-        <v>1549.89261911763</v>
+        <v>4.207224219928996</v>
       </c>
       <c r="C19" t="n">
-        <v>1629.044036715878</v>
+        <v>3.996886769057711</v>
       </c>
       <c r="D19" t="n">
-        <v>1634.599405148032</v>
+        <v>3.826277756039038</v>
       </c>
       <c r="E19" t="n">
-        <v>1540.005041008069</v>
+        <v>3.471199656989698</v>
       </c>
       <c r="F19" t="n">
-        <v>1333.982284734398</v>
+        <v>3.577298044465465</v>
       </c>
       <c r="G19" t="n">
-        <v>1006.277905219306</v>
+        <v>3.117528308207969</v>
       </c>
       <c r="H19" t="n">
-        <v>657.5064229646297</v>
+        <v>3.076626949890938</v>
       </c>
       <c r="I19" t="n">
-        <v>322.6610042876815</v>
+        <v>2.329921644973417</v>
       </c>
       <c r="J19" t="n">
-        <v>118.2324104260606</v>
+        <v>2.059942508493507</v>
       </c>
       <c r="K19" t="n">
-        <v>18.92306214359624</v>
+        <v>1.3470406959315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>577.41604</v>
+        <v>466.18943</v>
       </c>
       <c r="B20" t="n">
-        <v>472.5519161154585</v>
+        <v>0.04500930298329342</v>
       </c>
       <c r="C20" t="n">
-        <v>483.8338893067644</v>
+        <v>0.06476774502191805</v>
       </c>
       <c r="D20" t="n">
-        <v>475.2797554945989</v>
+        <v>-0.1991874708803549</v>
       </c>
       <c r="E20" t="n">
-        <v>434.4970815510083</v>
+        <v>0.1347576053536833</v>
       </c>
       <c r="F20" t="n">
-        <v>363.7640817725565</v>
+        <v>0.4281608963748949</v>
       </c>
       <c r="G20" t="n">
-        <v>265.8271767324803</v>
+        <v>0.4246206701080468</v>
       </c>
       <c r="H20" t="n">
-        <v>169.0062093406694</v>
+        <v>0.8288334187032742</v>
       </c>
       <c r="I20" t="n">
-        <v>79.4662798051328</v>
+        <v>0.682978349039089</v>
       </c>
       <c r="J20" t="n">
-        <v>29.31149494193329</v>
+        <v>0.9013085704334001</v>
       </c>
       <c r="K20" t="n">
-        <v>5.178835983757763</v>
+        <v>0.9040604112113428</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>577.50675</v>
+        <v>466.28723</v>
       </c>
       <c r="B21" t="n">
-        <v>184.2481053791719</v>
+        <v>0.4646373852673573</v>
       </c>
       <c r="C21" t="n">
-        <v>184.2008200208583</v>
+        <v>0.4756373269013919</v>
       </c>
       <c r="D21" t="n">
-        <v>178.0276940067837</v>
+        <v>0.4054557576708032</v>
       </c>
       <c r="E21" t="n">
-        <v>157.9316769214988</v>
+        <v>0.522960225838851</v>
       </c>
       <c r="F21" t="n">
-        <v>128.1997839877446</v>
+        <v>0.6414205613043574</v>
       </c>
       <c r="G21" t="n">
-        <v>84.74409960970068</v>
+        <v>0.5624756305615222</v>
       </c>
       <c r="H21" t="n">
-        <v>44.89852384607295</v>
+        <v>0.791756830826128</v>
       </c>
       <c r="I21" t="n">
-        <v>16.72208148911394</v>
+        <v>0.740472310003499</v>
       </c>
       <c r="J21" t="n">
-        <v>2.85012818466833</v>
+        <v>0.7891543327545318</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7841242309085068</v>
+        <v>0.8097950922090272</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>577.59745</v>
+        <v>466.38503</v>
       </c>
       <c r="B22" t="n">
-        <v>83.70031445377376</v>
+        <v>0.4273698929838304</v>
       </c>
       <c r="C22" t="n">
-        <v>83.55773131081587</v>
+        <v>0.2145407332708189</v>
       </c>
       <c r="D22" t="n">
-        <v>81.54582199088077</v>
+        <v>0.2364384791362041</v>
       </c>
       <c r="E22" t="n">
-        <v>74.64725186311495</v>
+        <v>0.1318951206964761</v>
       </c>
       <c r="F22" t="n">
-        <v>63.46428499244565</v>
+        <v>0.5490438379652489</v>
       </c>
       <c r="G22" t="n">
-        <v>45.82024452482791</v>
+        <v>0.6160885132512998</v>
       </c>
       <c r="H22" t="n">
-        <v>28.95805421169468</v>
+        <v>0.9412689255299986</v>
       </c>
       <c r="I22" t="n">
-        <v>14.90910470515892</v>
+        <v>0.8939129152700821</v>
       </c>
       <c r="J22" t="n">
-        <v>5.136394495694022</v>
+        <v>0.9712641593120347</v>
       </c>
       <c r="K22" t="n">
-        <v>1.565988255315043</v>
+        <v>0.8774394838688079</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>577.68815</v>
+        <v>466.48283</v>
       </c>
       <c r="B23" t="n">
-        <v>39.40818256883277</v>
+        <v>0.1879903758135858</v>
       </c>
       <c r="C23" t="n">
-        <v>38.67502422107736</v>
+        <v>0.1049634488742537</v>
       </c>
       <c r="D23" t="n">
-        <v>36.03640995600879</v>
+        <v>0.1514603018030237</v>
       </c>
       <c r="E23" t="n">
-        <v>29.64920244473702</v>
+        <v>0.1096641321460225</v>
       </c>
       <c r="F23" t="n">
-        <v>21.41253360803498</v>
+        <v>0.2048529683993415</v>
       </c>
       <c r="G23" t="n">
-        <v>13.0152294603345</v>
+        <v>0.2610690013632941</v>
       </c>
       <c r="H23" t="n">
-        <v>6.206144048433432</v>
+        <v>0.4790336240458394</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9969621820759</v>
+        <v>0.5351646603783056</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.05732511178665187</v>
+        <v>0.5340560086632657</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1842141855160559</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>577.7788399999999</v>
-      </c>
-      <c r="B24" t="n">
-        <v>21.15739894693895</v>
-      </c>
-      <c r="C24" t="n">
-        <v>21.29105996886568</v>
-      </c>
-      <c r="D24" t="n">
-        <v>19.19192436406514</v>
-      </c>
-      <c r="E24" t="n">
-        <v>15.74122636696091</v>
-      </c>
-      <c r="F24" t="n">
-        <v>11.65001091211684</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.77627584940295</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3.478811046428904</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.787497222035148</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.3263510708677392</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.02749125027359902</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>577.86952</v>
-      </c>
-      <c r="B25" t="n">
-        <v>13.87888575693946</v>
-      </c>
-      <c r="C25" t="n">
-        <v>13.12843280438684</v>
-      </c>
-      <c r="D25" t="n">
-        <v>11.18510505672772</v>
-      </c>
-      <c r="E25" t="n">
-        <v>10.45904139024287</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7.666898193558624</v>
-      </c>
-      <c r="G25" t="n">
-        <v>5.229828339662379</v>
-      </c>
-      <c r="H25" t="n">
-        <v>3.67704164574174</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.998065926085172</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.423778935479741</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.9869172445244395</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>577.9602</v>
-      </c>
-      <c r="B26" t="n">
-        <v>9.233974752378561</v>
-      </c>
-      <c r="C26" t="n">
-        <v>9.157267485680283</v>
-      </c>
-      <c r="D26" t="n">
-        <v>8.009748557824933</v>
-      </c>
-      <c r="E26" t="n">
-        <v>7.04944163124811</v>
-      </c>
-      <c r="F26" t="n">
-        <v>5.083784894738369</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.559660547054905</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.770261380410173</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.901915530518592</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.382757553100018</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1.166104474117458</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>578.05087</v>
-      </c>
-      <c r="B27" t="n">
-        <v>6.121524498256111</v>
-      </c>
-      <c r="C27" t="n">
-        <v>6.362344250016275</v>
-      </c>
-      <c r="D27" t="n">
-        <v>5.863324540206621</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4.978557675423091</v>
-      </c>
-      <c r="F27" t="n">
-        <v>3.779568278471183</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2.444021038257309</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.037050380218727</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.336935723793244</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.853708001236653</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.748028615302437</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>578.14154</v>
-      </c>
-      <c r="B28" t="n">
-        <v>4.938349547868272</v>
-      </c>
-      <c r="C28" t="n">
-        <v>5.217084197822679</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4.665822466376806</v>
-      </c>
-      <c r="E28" t="n">
-        <v>4.151593425293968</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.973586445578696</v>
-      </c>
-      <c r="G28" t="n">
-        <v>2.198652421198615</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1.534326566346708</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.8538210678374941</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.2389591554574342</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.1022057131507627</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>578.2322</v>
-      </c>
-      <c r="B29" t="n">
-        <v>3.024910045422685</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3.136159615606452</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2.696639765606344</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2.00829656065301</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.300246491783825</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.9531662878303834</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.5539280678219908</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.4370742372220762</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.124284234594381</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-0.1984882560745126</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>578.32285</v>
-      </c>
-      <c r="B30" t="n">
-        <v>3.49405774471183</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3.5157104888671</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3.172474276690732</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2.353904930550523</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.89977875845142</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.310641928144126</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.019158455653209</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.8467731517824092</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.7662609937448224</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.6816980314150221</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>578.4135</v>
-      </c>
-      <c r="B31" t="n">
-        <v>4.097123028863589</v>
-      </c>
-      <c r="C31" t="n">
-        <v>4.438299433528833</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4.248671598123378</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3.701257526368348</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.755297905403849</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.851993003830876</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1.3966627539992</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.9261175883633703</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0.9010607660713014</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.255353254776543</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>578.50414</v>
-      </c>
-      <c r="B32" t="n">
-        <v>3.032730307923317</v>
-      </c>
-      <c r="C32" t="n">
-        <v>3.248195392690616</v>
-      </c>
-      <c r="D32" t="n">
-        <v>3.07322322929571</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2.662951132300531</v>
-      </c>
-      <c r="F32" t="n">
-        <v>2.048238691547918</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.506031275199559</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.375829568122307</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.042562785126624</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.9805627408822803</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.8518363798201114</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>578.59478</v>
-      </c>
-      <c r="B33" t="n">
-        <v>2.759802288334698</v>
-      </c>
-      <c r="C33" t="n">
-        <v>2.468974817235853</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.081999165987742</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1.683228493009646</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.165844779416295</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1.294823730027803</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.621744355614533</v>
-      </c>
-      <c r="I33" t="n">
-        <v>1.650284557591114</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1.490602337695634</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1.026635716756082</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>578.68541</v>
-      </c>
-      <c r="B34" t="n">
-        <v>2.361542828470131</v>
-      </c>
-      <c r="C34" t="n">
-        <v>2.27779707914429</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.316497962297996</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2.378738191208156</v>
-      </c>
-      <c r="F34" t="n">
-        <v>2.028609823640609</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1.349195756465147</v>
-      </c>
-      <c r="H34" t="n">
-        <v>1.393034554509925</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1.476838505514835</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.476638033064712</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.515138443768294</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>578.77604</v>
-      </c>
-      <c r="B35" t="n">
-        <v>1.739431100612827</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1.223562719495747</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1.099311411611481</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.103403810672762</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.661249159588114</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1.413386082110138</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1.296315045033472</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.9294590856157965</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.7606371268660064</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.7841837639273634</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>578.86665</v>
-      </c>
-      <c r="B36" t="n">
-        <v>1.492066958894236</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.9973918237944195</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.3661363308751275</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.4754568562917004</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.9500151788617958</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1.193672959929524</v>
-      </c>
-      <c r="H36" t="n">
-        <v>1.302667039641485</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.7810035715366614</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.5684292393921858</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.5252576029912404</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>578.95727</v>
-      </c>
-      <c r="B37" t="n">
-        <v>1.384764820775973</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1.143463430418005</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0.690716902359543</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.6957037244563606</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0.7307149670115827</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.3515192138869299</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.2341995347648346</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09113401211954306</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.2691913733430267</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.4296396254114034</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>579.04787</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1.014351830979747</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1.2282521817041</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.366118905128829</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1.131871572919678</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1.270569247280621</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0.9763608835069383</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.7501255996243926</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.4592830721331949</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.5611990427962081</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.8224732967011219</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>579.13847</v>
-      </c>
-      <c r="B39" t="n">
-        <v>1.416694907326105</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1.791554552557332</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.072761508275227</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2.233293738021883</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1.97184583838858</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.802812656981123</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1.780991392851058</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1.225636826824845</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1.29555796231019</v>
-      </c>
-      <c r="K39" t="n">
-        <v>1.559704833288271</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>579.22907</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0.9501185536838356</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0.9403953876521264</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.002178072510081</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1.088758549285952</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.8931343983872567</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0.8192357497378773</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.8448483862982925</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.598351414921751</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.4663142477322544</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.3973079004483477</v>
+        <v>0.3908662486544394</v>
       </c>
     </row>
   </sheetData>
